--- a/public/templates/student.xlsx
+++ b/public/templates/student.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="308">
   <si>
     <t>6661204</t>
   </si>
@@ -883,9 +883,6 @@
   </si>
   <si>
     <t>Tích lũy 60 tín chỉ</t>
-  </si>
-  <si>
-    <t>Đăng ký nhầm mã HP, mã đúng là TH03298</t>
   </si>
   <si>
     <t>Tích lũy 72 tín chỉ</t>
@@ -955,13 +952,28 @@
   </si>
   <si>
     <t>28/03/04</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Đăng ký nhầm mã HP</t>
+  </si>
+  <si>
+    <t>0912121212</t>
+  </si>
+  <si>
+    <t>dvduy@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1118,6 +1130,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1453,7 +1473,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1499,8 +1519,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1546,8 +1567,15 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="43" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1581,6 +1609,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1868,7 +1897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="4" customWidth="1"/>
@@ -1881,46 +1910,54 @@
     <col min="8" max="8" width="42.42578125" style="4" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" style="4" customWidth="1"/>
     <col min="10" max="10" width="43.28515625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="46.140625" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="8.85546875" style="4"/>
+    <col min="11" max="11" width="27.28515625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" style="4" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="H1" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="G1" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="I1" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="K1" s="16" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+      <c r="M1" s="16" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>270</v>
       </c>
@@ -1943,7 +1980,7 @@
         <v>276</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>277</v>
@@ -1954,8 +1991,14 @@
       <c r="K2" s="7" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1969,7 +2012,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -1978,19 +2021,25 @@
         <v>209</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I3" s="3">
         <v>87</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -2013,19 +2062,21 @@
         <v>209</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I4" s="3">
         <v>82</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -2048,19 +2099,21 @@
         <v>209</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I5" s="3">
         <v>88</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -2083,19 +2136,21 @@
         <v>209</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I6" s="3">
         <v>90</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -2118,19 +2173,21 @@
         <v>209</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I7" s="3">
         <v>80</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -2153,19 +2210,21 @@
         <v>209</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I8" s="3">
         <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -2188,7 +2247,7 @@
         <v>210</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I9" s="3">
         <v>76</v>
@@ -2199,8 +2258,10 @@
       <c r="K9" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+    </row>
+    <row r="10" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -2223,7 +2284,7 @@
         <v>210</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I10" s="10">
         <v>73</v>
@@ -2232,10 +2293,12 @@
         <v>281</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -2258,7 +2321,7 @@
         <v>210</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I11" s="3">
         <v>63</v>
@@ -2269,8 +2332,10 @@
       <c r="K11" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -2293,7 +2358,7 @@
         <v>210</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I12" s="3">
         <v>77</v>
@@ -2304,8 +2369,10 @@
       <c r="K12" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -2328,7 +2395,7 @@
         <v>210</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I13" s="3">
         <v>70</v>
@@ -2339,8 +2406,10 @@
       <c r="K13" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -2363,7 +2432,7 @@
         <v>210</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I14" s="3">
         <v>63</v>
@@ -2374,8 +2443,10 @@
       <c r="K14" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -2398,19 +2469,21 @@
         <v>211</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I15" s="3">
         <v>89</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -2433,19 +2506,21 @@
         <v>211</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I16" s="3">
         <v>85</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -2468,19 +2543,21 @@
         <v>211</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I17" s="3">
         <v>79</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -2503,19 +2580,21 @@
         <v>211</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I18" s="3">
         <v>86</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -2538,19 +2617,21 @@
         <v>211</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I19" s="3">
         <v>91</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -2573,19 +2654,21 @@
         <v>211</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I20" s="3">
         <v>89</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -2608,19 +2691,21 @@
         <v>211</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I21" s="3">
         <v>83</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -2643,19 +2728,21 @@
         <v>211</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I22" s="3">
         <v>86</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -2678,19 +2765,21 @@
         <v>211</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I23" s="3">
         <v>91</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -2713,19 +2802,21 @@
         <v>212</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I24" s="3">
         <v>85</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -2748,19 +2839,21 @@
         <v>212</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I25" s="3">
         <v>76</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -2783,19 +2876,21 @@
         <v>212</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I26" s="3">
         <v>85</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -2818,19 +2913,21 @@
         <v>212</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I27" s="3">
         <v>94</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -2853,19 +2950,21 @@
         <v>212</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I28" s="3">
         <v>80</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -2888,19 +2987,21 @@
         <v>212</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I29" s="3">
         <v>75</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -2923,19 +3024,21 @@
         <v>212</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I30" s="3">
         <v>75</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -2958,19 +3061,21 @@
         <v>212</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I31" s="3">
         <v>79</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="17"/>
+      <c r="M31" s="17"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -2993,19 +3098,21 @@
         <v>212</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I32" s="3">
         <v>107</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -3028,19 +3135,21 @@
         <v>212</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I33" s="3">
         <v>79</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -3063,19 +3172,21 @@
         <v>212</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I34" s="3">
         <v>75</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -3098,19 +3209,21 @@
         <v>212</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I35" s="3">
         <v>78</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -3133,19 +3246,21 @@
         <v>208</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I36" s="3">
         <v>121</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" s="17"/>
+      <c r="M36" s="17"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -3168,19 +3283,21 @@
         <v>208</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I37" s="3">
         <v>115</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -3203,19 +3320,21 @@
         <v>208</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I38" s="3">
         <v>91</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -3238,19 +3357,21 @@
         <v>208</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I39" s="3">
         <v>98</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -3273,19 +3394,21 @@
         <v>208</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I40" s="3">
         <v>91</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -3308,19 +3431,21 @@
         <v>208</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I41" s="3">
         <v>92</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -3343,19 +3468,21 @@
         <v>208</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I42" s="3">
         <v>82</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -3378,19 +3505,21 @@
         <v>208</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I43" s="3">
         <v>87</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -3413,19 +3542,21 @@
         <v>208</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I44" s="3">
         <v>84</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -3448,19 +3579,21 @@
         <v>208</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I45" s="3">
         <v>106</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -3483,19 +3616,21 @@
         <v>208</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I46" s="3">
         <v>77</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -3518,19 +3653,21 @@
         <v>207</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I47" s="3">
         <v>63</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L47" s="17"/>
+      <c r="M47" s="17"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -3553,19 +3690,21 @@
         <v>207</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I48" s="3">
         <v>77</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -3588,19 +3727,21 @@
         <v>207</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I49" s="3">
         <v>64</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -3623,19 +3764,21 @@
         <v>207</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I50" s="3">
         <v>80</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L50" s="17"/>
+      <c r="M50" s="17"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -3658,19 +3801,21 @@
         <v>207</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I51" s="3">
         <v>74</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L51" s="17"/>
+      <c r="M51" s="17"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -3693,19 +3838,21 @@
         <v>207</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I52" s="3">
         <v>57</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>51</v>
       </c>
@@ -3728,19 +3875,21 @@
         <v>207</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I53" s="3">
         <v>54</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>52</v>
       </c>
@@ -3763,19 +3912,21 @@
         <v>207</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I54" s="3">
         <v>58</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>53</v>
       </c>
@@ -3798,19 +3949,21 @@
         <v>244</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I55" s="3">
         <v>87</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K55" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>54</v>
       </c>
@@ -3833,19 +3986,21 @@
         <v>244</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I56" s="3">
         <v>96</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K56" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>55</v>
       </c>
@@ -3868,19 +4023,21 @@
         <v>244</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I57" s="3">
         <v>84</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K57" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>56</v>
       </c>
@@ -3903,19 +4060,21 @@
         <v>244</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I58" s="3">
         <v>92</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K58" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>57</v>
       </c>
@@ -3938,19 +4097,21 @@
         <v>244</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I59" s="3">
         <v>89</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K59" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L59" s="17"/>
+      <c r="M59" s="17"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>58</v>
       </c>
@@ -3973,19 +4134,21 @@
         <v>244</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I60" s="3">
         <v>87</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K60" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>59</v>
       </c>
@@ -4008,19 +4171,21 @@
         <v>244</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I61" s="3">
         <v>84</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K61" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L61" s="17"/>
+      <c r="M61" s="17"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>60</v>
       </c>
@@ -4043,19 +4208,21 @@
         <v>244</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I62" s="3">
         <v>81</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>61</v>
       </c>
@@ -4078,19 +4245,21 @@
         <v>244</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I63" s="3">
         <v>74</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K63" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L63" s="17"/>
+      <c r="M63" s="17"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>62</v>
       </c>
@@ -4113,19 +4282,21 @@
         <v>244</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I64" s="3">
         <v>77</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K64" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>63</v>
       </c>
@@ -4148,19 +4319,21 @@
         <v>244</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I65" s="3">
         <v>77</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K65" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L65" s="17"/>
+      <c r="M65" s="17"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>64</v>
       </c>
@@ -4183,19 +4356,21 @@
         <v>269</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I66" s="3">
         <v>76</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K66" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L66" s="17"/>
+      <c r="M66" s="17"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>65</v>
       </c>
@@ -4218,19 +4393,21 @@
         <v>269</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I67" s="3">
         <v>94</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K67" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L67" s="17"/>
+      <c r="M67" s="17"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>66</v>
       </c>
@@ -4253,19 +4430,21 @@
         <v>269</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I68" s="3">
         <v>75</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K68" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L68" s="17"/>
+      <c r="M68" s="17"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>67</v>
       </c>
@@ -4288,19 +4467,21 @@
         <v>269</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I69" s="3">
         <v>94</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K69" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L69" s="17"/>
+      <c r="M69" s="17"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>68</v>
       </c>
@@ -4323,19 +4504,21 @@
         <v>269</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I70" s="3">
         <v>86</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K70" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L70" s="17"/>
+      <c r="M70" s="17"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>69</v>
       </c>
@@ -4358,19 +4541,21 @@
         <v>269</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I71" s="3">
         <v>85</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K71" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>70</v>
       </c>
@@ -4393,19 +4578,21 @@
         <v>269</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I72" s="3">
         <v>78</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K72" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>71</v>
       </c>
@@ -4428,19 +4615,21 @@
         <v>269</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I73" s="3">
         <v>86</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K73" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L73" s="17"/>
+      <c r="M73" s="17"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>72</v>
       </c>
@@ -4463,19 +4652,21 @@
         <v>269</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3">
         <v>91</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K74" s="5" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L74" s="17"/>
+      <c r="M74" s="17"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>73</v>
       </c>
@@ -4498,21 +4689,29 @@
         <v>269</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I75" s="3">
         <v>101</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K75" s="5" t="s">
         <v>280</v>
       </c>
+      <c r="L75" s="17"/>
+      <c r="M75" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:K75"/>
+  <sortState ref="A3:M75">
+    <sortCondition ref="L2"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="M3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/templates/student.xlsx
+++ b/public/templates/student.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hueph\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hueph\Desktop\KLTN\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -963,10 +963,10 @@
     <t>Đăng ký nhầm mã HP</t>
   </si>
   <si>
-    <t>0912121212</t>
-  </si>
-  <si>
     <t>dvduy@gmail.com</t>
+  </si>
+  <si>
+    <t>0987654321</t>
   </si>
 </sst>
 </file>
@@ -2033,10 +2033,10 @@
         <v>280</v>
       </c>
       <c r="L3" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="M3" s="21" t="s">
         <v>306</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">

--- a/public/templates/student.xlsx
+++ b/public/templates/student.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hueph\Desktop\KLTN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hueph\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -928,9 +928,6 @@
 (Bắt buộc)</t>
   </si>
   <si>
-    <t>dd/MM/yy</t>
-  </si>
-  <si>
     <t>Kiểu chuỗi/10
 (Bắt buộc)</t>
   </si>
@@ -963,10 +960,15 @@
     <t>Đăng ký nhầm mã HP</t>
   </si>
   <si>
+    <t>0912121212</t>
+  </si>
+  <si>
     <t>dvduy@gmail.com</t>
   </si>
   <si>
-    <t>0987654321</t>
+    <t>Kiểu chuỗi
+dd/MM/yy
+(Bắt buộc)</t>
   </si>
 </sst>
 </file>
@@ -1559,9 +1561,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1574,6 +1573,9 @@
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="43" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1917,44 +1919,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="G1" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="K1" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="I1" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="K1" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>301</v>
+      <c r="M1" s="15" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="33" x14ac:dyDescent="0.25">
@@ -1991,11 +1993,11 @@
       <c r="K2" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>303</v>
-      </c>
-      <c r="M2" s="19" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -2012,7 +2014,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -2032,10 +2034,10 @@
       <c r="K3" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L3" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="M3" s="21" t="s">
+      <c r="L3" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="M3" s="20" t="s">
         <v>306</v>
       </c>
     </row>
@@ -2073,8 +2075,8 @@
       <c r="K4" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -2110,8 +2112,8 @@
       <c r="K5" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -2147,8 +2149,8 @@
       <c r="K6" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -2184,8 +2186,8 @@
       <c r="K7" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -2221,8 +2223,8 @@
       <c r="K8" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -2258,8 +2260,8 @@
       <c r="K9" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
     </row>
     <row r="10" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
@@ -2293,10 +2295,10 @@
         <v>281</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
+        <v>304</v>
+      </c>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -2332,8 +2334,8 @@
       <c r="K11" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -2369,8 +2371,8 @@
       <c r="K12" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -2406,8 +2408,8 @@
       <c r="K13" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -2443,8 +2445,8 @@
       <c r="K14" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -2480,8 +2482,8 @@
       <c r="K15" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -2517,8 +2519,8 @@
       <c r="K16" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -2554,8 +2556,8 @@
       <c r="K17" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -2591,8 +2593,8 @@
       <c r="K18" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -2628,8 +2630,8 @@
       <c r="K19" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -2665,8 +2667,8 @@
       <c r="K20" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -2702,8 +2704,8 @@
       <c r="K21" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -2739,8 +2741,8 @@
       <c r="K22" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
@@ -2776,8 +2778,8 @@
       <c r="K23" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -2813,8 +2815,8 @@
       <c r="K24" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -2850,8 +2852,8 @@
       <c r="K25" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -2887,8 +2889,8 @@
       <c r="K26" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
@@ -2924,8 +2926,8 @@
       <c r="K27" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
@@ -2961,8 +2963,8 @@
       <c r="K28" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
@@ -2998,8 +3000,8 @@
       <c r="K29" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
@@ -3035,8 +3037,8 @@
       <c r="K30" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
@@ -3072,8 +3074,8 @@
       <c r="K31" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
@@ -3109,8 +3111,8 @@
       <c r="K32" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
@@ -3146,8 +3148,8 @@
       <c r="K33" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
@@ -3183,8 +3185,8 @@
       <c r="K34" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
@@ -3220,8 +3222,8 @@
       <c r="K35" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
@@ -3257,8 +3259,8 @@
       <c r="K36" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
@@ -3294,8 +3296,8 @@
       <c r="K37" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
@@ -3331,8 +3333,8 @@
       <c r="K38" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
@@ -3368,8 +3370,8 @@
       <c r="K39" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
@@ -3405,8 +3407,8 @@
       <c r="K40" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
@@ -3442,8 +3444,8 @@
       <c r="K41" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
@@ -3479,8 +3481,8 @@
       <c r="K42" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
@@ -3516,8 +3518,8 @@
       <c r="K43" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
@@ -3553,8 +3555,8 @@
       <c r="K44" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
@@ -3590,8 +3592,8 @@
       <c r="K45" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
@@ -3627,8 +3629,8 @@
       <c r="K46" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="L46" s="17"/>
-      <c r="M46" s="17"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
@@ -3664,8 +3666,8 @@
       <c r="K47" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L47" s="17"/>
-      <c r="M47" s="17"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
@@ -3701,8 +3703,8 @@
       <c r="K48" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
@@ -3738,8 +3740,8 @@
       <c r="K49" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
@@ -3775,8 +3777,8 @@
       <c r="K50" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
@@ -3812,8 +3814,8 @@
       <c r="K51" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
@@ -3849,8 +3851,8 @@
       <c r="K52" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
@@ -3886,8 +3888,8 @@
       <c r="K53" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
@@ -3923,8 +3925,8 @@
       <c r="K54" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L54" s="17"/>
-      <c r="M54" s="17"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
@@ -3960,8 +3962,8 @@
       <c r="K55" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
@@ -3997,8 +3999,8 @@
       <c r="K56" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
@@ -4034,8 +4036,8 @@
       <c r="K57" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
@@ -4071,8 +4073,8 @@
       <c r="K58" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
@@ -4108,8 +4110,8 @@
       <c r="K59" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
@@ -4145,8 +4147,8 @@
       <c r="K60" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
@@ -4182,8 +4184,8 @@
       <c r="K61" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
@@ -4219,8 +4221,8 @@
       <c r="K62" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
@@ -4256,8 +4258,8 @@
       <c r="K63" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
@@ -4293,8 +4295,8 @@
       <c r="K64" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L64" s="17"/>
-      <c r="M64" s="17"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
@@ -4330,8 +4332,8 @@
       <c r="K65" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
+      <c r="L65" s="16"/>
+      <c r="M65" s="16"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
@@ -4367,8 +4369,8 @@
       <c r="K66" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L66" s="17"/>
-      <c r="M66" s="17"/>
+      <c r="L66" s="16"/>
+      <c r="M66" s="16"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
@@ -4404,8 +4406,8 @@
       <c r="K67" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L67" s="17"/>
-      <c r="M67" s="17"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
@@ -4441,8 +4443,8 @@
       <c r="K68" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L68" s="17"/>
-      <c r="M68" s="17"/>
+      <c r="L68" s="16"/>
+      <c r="M68" s="16"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
@@ -4478,8 +4480,8 @@
       <c r="K69" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L69" s="17"/>
-      <c r="M69" s="17"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
@@ -4515,8 +4517,8 @@
       <c r="K70" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L70" s="17"/>
-      <c r="M70" s="17"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
@@ -4552,8 +4554,8 @@
       <c r="K71" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
@@ -4589,8 +4591,8 @@
       <c r="K72" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L72" s="17"/>
-      <c r="M72" s="17"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
@@ -4626,8 +4628,8 @@
       <c r="K73" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L73" s="17"/>
-      <c r="M73" s="17"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
@@ -4663,8 +4665,8 @@
       <c r="K74" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L74" s="17"/>
-      <c r="M74" s="17"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
@@ -4700,8 +4702,8 @@
       <c r="K75" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="L75" s="17"/>
-      <c r="M75" s="17"/>
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:K75"/>
